--- a/Data_processed/env_yr.xlsx
+++ b/Data_processed/env_yr.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GDrive\Academicos\Articulos\Pendientes\Varadero growth rates\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GDrive\Academicos\Articulos\Pendientes\Varadero growth rates\Data_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D3370E-FE41-4F4E-B45F-B9E30CE83629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299EA2B4-71C7-4F21-8AFC-291A951100B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EC6B3B9-CD09-474A-97A4-BF889824A090}"/>
+    <workbookView xWindow="1392" yWindow="612" windowWidth="17280" windowHeight="10332" xr2:uid="{2EC6B3B9-CD09-474A-97A4-BF889824A090}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -30,7 +41,7 @@
     <author>Luis Lizcano</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{41A19E59-6F23-41F8-BF3D-1242E0C19A0F}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{41A19E59-6F23-41F8-BF3D-1242E0C19A0F}">
       <text>
         <r>
           <rPr>
@@ -59,21 +70,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Year</t>
-  </si>
-  <si>
-    <t>WaterFlow</t>
-  </si>
-  <si>
-    <t>Temperature</t>
   </si>
   <si>
     <t>SOI</t>
   </si>
   <si>
     <t>AMO</t>
+  </si>
+  <si>
+    <t>Air_Temperature</t>
+  </si>
+  <si>
+    <t>SST_CCI</t>
+  </si>
+  <si>
+    <t>HadISST</t>
+  </si>
+  <si>
+    <t>WF_Helena</t>
+  </si>
+  <si>
+    <t>WF_Calamar</t>
   </si>
 </sst>
 </file>
@@ -147,6 +167,2934 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>WaterFlow</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>WF_Helena</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$A$2:$A$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1981</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$B$2:$B$36</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>259.74166666666667</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>326.30833333333334</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>294.05</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>356.47499999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>515.89166666666677</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>465.34166666666653</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>419.25833333333338</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>560.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>512.25833333333333</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>482.4083333333333</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>401.79999999999995</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>370.78333333333336</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>366.98333333333335</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>361.55833333333334</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>284.84999999999997</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>511.77500000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>537.83333333333337</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>358.34166666666664</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>214.61666666666665</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>407.42499999999995</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>391.52500000000003</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>384.99999999999994</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>324.16666666666669</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>248.8416666666667</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>242.79999999999998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>316.10833333333335</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>369.30833333333334</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>437.18333333333334</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>312.54166666666669</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>317.27500000000003</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>304.03333333333336</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>362.58333333333331</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>157.01666666666668</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>239.70833333333334</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>256.24583333333334</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-431C-467D-97FD-06415FD7A0AE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1962622880"/>
+        <c:axId val="1962621440"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>WF_Calamar</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$A$2:$A$63</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="62"/>
+                <c:pt idx="0">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1974</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1973</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1972</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1971</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1970</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1969</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1968</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1967</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1966</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1965</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1964</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1963</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1962</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1961</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1960</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1959</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1958</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1957</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1956</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1955</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1954</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$C$2:$C$63</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="62"/>
+                <c:pt idx="0">
+                  <c:v>4608.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5799.083333333333</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6146.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7361.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10223.916666666666</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9012.1666666666661</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6946.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9878.4166666666661</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8904.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8022.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7210.166666666667</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6657.833333333333</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6293.666666666667</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5473.25</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5162.333333333333</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8423.1666666666661</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10123.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6857</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4667.833333333333</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8578.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6814.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7598.083333333333</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6861.916666666667</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5090.166666666667</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6351.75</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7076</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>8372.5833333333339</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8442.25</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6941.25</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7595.166666666667</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6495.833333333333</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8824.1666666666661</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5919.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7746.166666666667</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>9255.3333333333339</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>6208.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7326.75</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>6900.75</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>5718</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7073.833333333333</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8841</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8906.5833333333339</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>6785.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>7173.75</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>10321.083333333334</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8388.8333333333339</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>7425.666666666667</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>7191.583333333333</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>7275.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>7130.166666666667</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5808.666666666667</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>7291</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>7493.166666666667</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>7847.75</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>6466</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>7080.833333333333</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5683.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4849.333333333333</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5915.166666666667</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>8566.4</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8441.6</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>7888.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-431C-467D-97FD-06415FD7A0AE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1962636320"/>
+        <c:axId val="1962638240"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1962622880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1962621440"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1962621440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Waterflow</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" b="1" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> Sta Helena</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1962622880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1962638240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="4000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Waterflow Calamar</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1962636320"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1962636320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1962638240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.0355205599300086E-2"/>
+                  <c:y val="-0.11943642461358997"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$B$2:$B$36</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>259.74166666666667</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>326.30833333333334</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>294.05</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>356.47499999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>515.89166666666677</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>465.34166666666653</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>419.25833333333338</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>560.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>512.25833333333333</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>482.4083333333333</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>401.79999999999995</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>370.78333333333336</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>366.98333333333335</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>361.55833333333334</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>284.84999999999997</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>511.77500000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>537.83333333333337</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>358.34166666666664</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>214.61666666666665</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>407.42499999999995</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>391.52500000000003</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>384.99999999999994</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>324.16666666666669</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>248.8416666666667</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>242.79999999999998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>316.10833333333335</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>369.30833333333334</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>437.18333333333334</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>312.54166666666669</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>317.27500000000003</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>304.03333333333336</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>362.58333333333331</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>157.01666666666668</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>239.70833333333334</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>256.24583333333334</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$C$2:$C$36</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>4608.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5799.083333333333</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6146.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7361.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10223.916666666666</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9012.1666666666661</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6946.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9878.4166666666661</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8904.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8022.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7210.166666666667</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6657.833333333333</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6293.666666666667</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5473.25</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5162.333333333333</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8423.1666666666661</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10123.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6857</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4667.833333333333</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8578.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6814.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7598.083333333333</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6861.916666666667</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5090.166666666667</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6351.75</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7076</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>8372.5833333333339</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8442.25</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6941.25</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7595.166666666667</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6495.833333333333</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8824.1666666666661</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5919.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7746.166666666667</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>9255.3333333333339</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3609-4A4D-BA47-E27C080A2D52}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="214188992"/>
+        <c:axId val="214184192"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="214188992"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="214184192"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="214184192"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="214188992"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>291465</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0BE7DFA-56AF-E9E0-AF78-254AC624F569}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>110490</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>110490</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C6DC637-FE38-21E9-873A-DDECEC14251D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -446,18 +3394,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55147CBF-E4E8-4069-AAA0-07637B0B923A}">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="16.109375" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -465,42 +3420,69 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2015</v>
       </c>
       <c r="B2" s="1">
         <v>259.74166666666667</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
+        <v>4608.416666666667</v>
+      </c>
+      <c r="D2" s="2">
         <v>28.392886867412198</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
+        <v>28.973333333333333</v>
+      </c>
+      <c r="F2" s="1">
+        <v>28.440627333333328</v>
+      </c>
+      <c r="G2" s="1">
         <v>-0.79166666666666663</v>
       </c>
-      <c r="E2" s="1">
+      <c r="H2" s="1">
         <v>0.10616666666666667</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2014</v>
       </c>
       <c r="B3" s="1">
         <v>326.30833333333334</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
+        <v>5799.083333333333</v>
+      </c>
+      <c r="D3" s="2">
         <v>28.249761100998459</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
+        <v>29.071916666666667</v>
+      </c>
+      <c r="F3" s="1">
+        <v>28.350333750000001</v>
+      </c>
+      <c r="G3" s="1">
         <v>-0.13333333333333333</v>
       </c>
-      <c r="E3" s="1">
+      <c r="H3" s="1">
         <v>9.3750000000000014E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2013</v>
       </c>
@@ -508,16 +3490,25 @@
         <v>294.05</v>
       </c>
       <c r="C4" s="1">
+        <v>6146.416666666667</v>
+      </c>
+      <c r="D4" s="1">
         <v>28.191666666666666</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
+        <v>29.067750000000004</v>
+      </c>
+      <c r="F4" s="1">
+        <v>28.374319166666666</v>
+      </c>
+      <c r="G4" s="1">
         <v>0.45</v>
       </c>
-      <c r="E4" s="1">
+      <c r="H4" s="1">
         <v>0.1585</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2012</v>
       </c>
@@ -525,16 +3516,25 @@
         <v>356.47499999999997</v>
       </c>
       <c r="C5" s="1">
+        <v>7361.5</v>
+      </c>
+      <c r="D5" s="1">
         <v>28.141176055555551</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
+        <v>28.99175</v>
+      </c>
+      <c r="F5" s="1">
+        <v>28.288394166666663</v>
+      </c>
+      <c r="G5" s="1">
         <v>0.13333333333333333</v>
       </c>
-      <c r="E5" s="1">
+      <c r="H5" s="1">
         <v>0.20516666666666664</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2011</v>
       </c>
@@ -542,16 +3542,25 @@
         <v>515.89166666666677</v>
       </c>
       <c r="C6" s="1">
+        <v>10223.916666666666</v>
+      </c>
+      <c r="D6" s="1">
         <v>27.712500000000002</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
+        <v>28.974166666666665</v>
+      </c>
+      <c r="F6" s="1">
+        <v>28.450184916666672</v>
+      </c>
+      <c r="G6" s="1">
         <v>1.4000000000000001</v>
       </c>
-      <c r="E6" s="1">
+      <c r="H6" s="1">
         <v>9.3666666666666662E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2010</v>
       </c>
@@ -559,16 +3568,25 @@
         <v>465.34166666666653</v>
       </c>
       <c r="C7" s="1">
+        <v>9012.1666666666661</v>
+      </c>
+      <c r="D7" s="1">
         <v>28.133333333333329</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
+        <v>29.084999999999997</v>
+      </c>
+      <c r="F7" s="1">
+        <v>28.788282833333337</v>
+      </c>
+      <c r="G7" s="1">
         <v>0.90833333333333366</v>
       </c>
-      <c r="E7" s="1">
+      <c r="H7" s="1">
         <v>0.34116666666666667</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2009</v>
       </c>
@@ -576,16 +3594,25 @@
         <v>419.25833333333338</v>
       </c>
       <c r="C8" s="1">
+        <v>6946.25</v>
+      </c>
+      <c r="D8" s="1">
         <v>28.166666666666661</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
+        <v>28.939333333333334</v>
+      </c>
+      <c r="F8" s="1">
+        <v>28.157397416666672</v>
+      </c>
+      <c r="G8" s="1">
         <v>0.16666666666666666</v>
       </c>
-      <c r="E8" s="1">
+      <c r="H8" s="1">
         <v>3.0416666666666651E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2008</v>
       </c>
@@ -593,16 +3620,25 @@
         <v>560.5</v>
       </c>
       <c r="C9" s="1">
+        <v>9878.4166666666661</v>
+      </c>
+      <c r="D9" s="1">
         <v>27.633333333333329</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="1">
+        <v>28.784749999999999</v>
+      </c>
+      <c r="F9" s="1">
+        <v>28.190558999999997</v>
+      </c>
+      <c r="G9" s="1">
         <v>1.125</v>
       </c>
-      <c r="E9" s="1">
+      <c r="H9" s="1">
         <v>0.12925</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2007</v>
       </c>
@@ -610,16 +3646,25 @@
         <v>512.25833333333333</v>
       </c>
       <c r="C10" s="1">
+        <v>8904.25</v>
+      </c>
+      <c r="D10" s="1">
         <v>27.775000000000002</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
+        <v>29.008499999999998</v>
+      </c>
+      <c r="F10" s="1">
+        <v>28.262998833333338</v>
+      </c>
+      <c r="G10" s="1">
         <v>0.26666666666666661</v>
       </c>
-      <c r="E10" s="1">
+      <c r="H10" s="1">
         <v>0.13841666666666666</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2006</v>
       </c>
@@ -627,16 +3672,25 @@
         <v>482.4083333333333</v>
       </c>
       <c r="C11" s="1">
+        <v>8022.416666666667</v>
+      </c>
+      <c r="D11" s="1">
         <v>27.974999999999998</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
+        <v>29.035083333333336</v>
+      </c>
+      <c r="F11" s="1">
+        <v>28.380702249999999</v>
+      </c>
+      <c r="G11" s="1">
         <v>2.4999999999999984E-2</v>
       </c>
-      <c r="E11" s="1">
+      <c r="H11" s="1">
         <v>0.25741666666666668</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2005</v>
       </c>
@@ -644,16 +3698,25 @@
         <v>401.79999999999995</v>
       </c>
       <c r="C12" s="1">
+        <v>7210.166666666667</v>
+      </c>
+      <c r="D12" s="1">
         <v>28.133333333333336</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
+        <v>29.096916666666669</v>
+      </c>
+      <c r="F12" s="1">
+        <v>28.57411333333334</v>
+      </c>
+      <c r="G12" s="1">
         <v>-0.18333333333333338</v>
       </c>
-      <c r="E12" s="1">
+      <c r="H12" s="1">
         <v>0.28266666666666668</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2004</v>
       </c>
@@ -661,16 +3724,25 @@
         <v>370.78333333333336</v>
       </c>
       <c r="C13" s="1">
+        <v>6657.833333333333</v>
+      </c>
+      <c r="D13" s="1">
         <v>27.858333333333331</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
+        <v>28.828000000000003</v>
+      </c>
+      <c r="F13" s="1">
+        <v>28.312259916666665</v>
+      </c>
+      <c r="G13" s="1">
         <v>-0.25833333333333336</v>
       </c>
-      <c r="E13" s="1">
+      <c r="H13" s="1">
         <v>0.19674999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2003</v>
       </c>
@@ -678,16 +3750,25 @@
         <v>366.98333333333335</v>
       </c>
       <c r="C14" s="1">
+        <v>6293.666666666667</v>
+      </c>
+      <c r="D14" s="1">
         <v>28.025000000000002</v>
       </c>
-      <c r="D14" s="1">
+      <c r="E14" s="1">
+        <v>29.16491666666667</v>
+      </c>
+      <c r="F14" s="1">
+        <v>28.342821500000003</v>
+      </c>
+      <c r="G14" s="1">
         <v>-9.166666666666666E-2</v>
       </c>
-      <c r="E14" s="1">
+      <c r="H14" s="1">
         <v>0.22158333333333335</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2002</v>
       </c>
@@ -695,16 +3776,25 @@
         <v>361.55833333333334</v>
       </c>
       <c r="C15" s="1">
+        <v>5473.25</v>
+      </c>
+      <c r="D15" s="1">
         <v>28.049999999999997</v>
       </c>
-      <c r="D15" s="1">
+      <c r="E15" s="1">
+        <v>28.948583333333332</v>
+      </c>
+      <c r="F15" s="1">
+        <v>28.124589</v>
+      </c>
+      <c r="G15" s="1">
         <v>-0.3249999999999999</v>
       </c>
-      <c r="E15" s="1">
+      <c r="H15" s="1">
         <v>5.5333333333333345E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2001</v>
       </c>
@@ -712,16 +3802,25 @@
         <v>284.84999999999997</v>
       </c>
       <c r="C16" s="1">
+        <v>5162.333333333333</v>
+      </c>
+      <c r="D16" s="1">
         <v>27.708333333333332</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="1">
+        <v>28.476000000000003</v>
+      </c>
+      <c r="F16" s="1">
+        <v>28.085139333333334</v>
+      </c>
+      <c r="G16" s="1">
         <v>0.2583333333333333</v>
       </c>
-      <c r="E16" s="1">
+      <c r="H16" s="1">
         <v>0.10933333333333332</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2000</v>
       </c>
@@ -729,16 +3828,25 @@
         <v>511.77500000000003</v>
       </c>
       <c r="C17" s="1">
+        <v>8423.1666666666661</v>
+      </c>
+      <c r="D17" s="1">
         <v>27.383333333333336</v>
       </c>
-      <c r="D17" s="1">
+      <c r="E17" s="1">
+        <v>28.357416666666662</v>
+      </c>
+      <c r="F17" s="1">
+        <v>27.965294249999996</v>
+      </c>
+      <c r="G17" s="1">
         <v>0.85</v>
       </c>
-      <c r="E17" s="1">
+      <c r="H17" s="1">
         <v>1.8583333333333327E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1999</v>
       </c>
@@ -746,16 +3854,25 @@
         <v>537.83333333333337</v>
       </c>
       <c r="C18" s="1">
+        <v>10123.5</v>
+      </c>
+      <c r="D18" s="1">
         <v>27.408333333333335</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="1">
+        <v>28.742500000000003</v>
+      </c>
+      <c r="F18" s="1">
+        <v>28.090008666666666</v>
+      </c>
+      <c r="G18" s="1">
         <v>0.85</v>
       </c>
-      <c r="E18" s="1">
+      <c r="H18" s="1">
         <v>0.108</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1998</v>
       </c>
@@ -763,16 +3880,25 @@
         <v>358.34166666666664</v>
       </c>
       <c r="C19" s="1">
+        <v>6857</v>
+      </c>
+      <c r="D19" s="1">
         <v>28.099999999999998</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="1">
+        <v>29.235416666666666</v>
+      </c>
+      <c r="F19" s="1">
+        <v>28.547718249999999</v>
+      </c>
+      <c r="G19" s="1">
         <v>-2.4999999999999984E-2</v>
       </c>
-      <c r="E19" s="1">
+      <c r="H19" s="1">
         <v>0.36258333333333331</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1997</v>
       </c>
@@ -780,16 +3906,25 @@
         <v>214.61666666666665</v>
       </c>
       <c r="C20" s="1">
+        <v>4667.833333333333</v>
+      </c>
+      <c r="D20" s="1">
         <v>27.766666666666666</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E20" s="1">
+        <v>28.717833333333328</v>
+      </c>
+      <c r="F20" s="1">
+        <v>28.190484333333341</v>
+      </c>
+      <c r="G20" s="1">
         <v>-0.73333333333333339</v>
       </c>
-      <c r="E20" s="1">
+      <c r="H20" s="1">
         <v>4.200000000000001E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1996</v>
       </c>
@@ -797,16 +3932,25 @@
         <v>407.42499999999995</v>
       </c>
       <c r="C21" s="1">
+        <v>8578.5</v>
+      </c>
+      <c r="D21" s="1">
         <v>27.691666666666666</v>
       </c>
-      <c r="D21" s="1">
+      <c r="E21" s="1">
+        <v>28.69875</v>
+      </c>
+      <c r="F21" s="1">
+        <v>28.181941166666665</v>
+      </c>
+      <c r="G21" s="1">
         <v>0.67500000000000016</v>
       </c>
-      <c r="E21" s="1">
+      <c r="H21" s="1">
         <v>-6.7750000000000019E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1995</v>
       </c>
@@ -814,16 +3958,25 @@
         <v>391.52500000000003</v>
       </c>
       <c r="C22" s="1">
+        <v>6814.5</v>
+      </c>
+      <c r="D22" s="1">
         <v>27.791666666666668</v>
       </c>
-      <c r="D22" s="1">
+      <c r="E22" s="1">
+        <v>29.121916666666667</v>
+      </c>
+      <c r="F22" s="1">
+        <v>28.347782166666672</v>
+      </c>
+      <c r="G22" s="1">
         <v>-1.6666666666666666E-2</v>
       </c>
-      <c r="E22" s="1">
+      <c r="H22" s="1">
         <v>0.12491666666666666</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1994</v>
       </c>
@@ -831,16 +3984,25 @@
         <v>384.99999999999994</v>
       </c>
       <c r="C23" s="1">
+        <v>7598.083333333333</v>
+      </c>
+      <c r="D23" s="1">
         <v>27.5</v>
       </c>
-      <c r="D23" s="1">
+      <c r="E23" s="1">
+        <v>28.734916666666663</v>
+      </c>
+      <c r="F23" s="1">
+        <v>27.953286166666672</v>
+      </c>
+      <c r="G23" s="1">
         <v>-0.82499999999999984</v>
       </c>
-      <c r="E23" s="1">
+      <c r="H23" s="1">
         <v>-0.1869166666666667</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1993</v>
       </c>
@@ -848,16 +4010,25 @@
         <v>324.16666666666669</v>
       </c>
       <c r="C24" s="1">
+        <v>6861.916666666667</v>
+      </c>
+      <c r="D24" s="1">
         <v>27.791666666666668</v>
       </c>
-      <c r="D24" s="1">
+      <c r="E24" s="1">
+        <v>28.96916666666667</v>
+      </c>
+      <c r="F24" s="1">
+        <v>28.17655091666667</v>
+      </c>
+      <c r="G24" s="1">
         <v>-0.65</v>
       </c>
-      <c r="E24" s="1">
+      <c r="H24" s="1">
         <v>-0.22058333333333333</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1992</v>
       </c>
@@ -865,16 +4036,25 @@
         <v>248.8416666666667</v>
       </c>
       <c r="C25" s="1">
+        <v>5090.166666666667</v>
+      </c>
+      <c r="D25" s="1">
         <v>27.775000000000002</v>
       </c>
-      <c r="D25" s="1">
+      <c r="E25" s="1">
+        <v>28.461166666666667</v>
+      </c>
+      <c r="F25" s="1">
+        <v>27.949361333333332</v>
+      </c>
+      <c r="G25" s="1">
         <v>-0.82500000000000007</v>
       </c>
-      <c r="E25" s="1">
+      <c r="H25" s="1">
         <v>-0.22925000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1991</v>
       </c>
@@ -882,16 +4062,25 @@
         <v>242.79999999999998</v>
       </c>
       <c r="C26" s="1">
+        <v>6351.75</v>
+      </c>
+      <c r="D26" s="1">
         <v>27.625</v>
       </c>
-      <c r="D26" s="1">
+      <c r="E26" s="1">
+        <v>28.362583333333333</v>
+      </c>
+      <c r="F26" s="1">
+        <v>27.809265416666662</v>
+      </c>
+      <c r="G26" s="1">
         <v>-0.57500000000000007</v>
       </c>
-      <c r="E26" s="1">
+      <c r="H26" s="1">
         <v>-0.14241666666666669</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1990</v>
       </c>
@@ -899,16 +4088,25 @@
         <v>316.10833333333335</v>
       </c>
       <c r="C27" s="1">
+        <v>7076</v>
+      </c>
+      <c r="D27" s="1">
         <v>27.474999999999998</v>
       </c>
-      <c r="D27" s="1">
+      <c r="E27" s="1">
+        <v>28.599166666666665</v>
+      </c>
+      <c r="F27" s="1">
+        <v>27.990827583333331</v>
+      </c>
+      <c r="G27" s="1">
         <v>-0.11666666666666665</v>
       </c>
-      <c r="E27" s="1">
+      <c r="H27" s="1">
         <v>-4.8583333333333333E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1989</v>
       </c>
@@ -916,16 +4114,25 @@
         <v>369.30833333333334</v>
       </c>
       <c r="C28" s="1">
+        <v>8372.5833333333339</v>
+      </c>
+      <c r="D28" s="1">
         <v>27.574999999999999</v>
       </c>
-      <c r="D28" s="1">
+      <c r="E28" s="1">
+        <v>28.467916666666667</v>
+      </c>
+      <c r="F28" s="1">
+        <v>27.677340916666665</v>
+      </c>
+      <c r="G28" s="1">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E28" s="1">
+      <c r="H28" s="1">
         <v>-9.3083333333333337E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1988</v>
       </c>
@@ -933,16 +4140,25 @@
         <v>437.18333333333334</v>
       </c>
       <c r="C29" s="1">
+        <v>8442.25</v>
+      </c>
+      <c r="D29" s="1">
         <v>27.508333333333336</v>
       </c>
-      <c r="D29" s="1">
+      <c r="E29" s="1">
+        <v>28.414333333333335</v>
+      </c>
+      <c r="F29" s="1">
+        <v>28.125297499999999</v>
+      </c>
+      <c r="G29" s="1">
         <v>0.81666666666666654</v>
       </c>
-      <c r="E29" s="1">
+      <c r="H29" s="1">
         <v>-1.5166666666666674E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1987</v>
       </c>
@@ -950,16 +4166,25 @@
         <v>312.54166666666669</v>
       </c>
       <c r="C30" s="1">
+        <v>6941.25</v>
+      </c>
+      <c r="D30" s="1">
         <v>27.966666666666669</v>
       </c>
-      <c r="D30" s="1">
+      <c r="E30" s="1">
+        <v>28.551333333333336</v>
+      </c>
+      <c r="F30" s="1">
+        <v>28.320948583333333</v>
+      </c>
+      <c r="G30" s="1">
         <v>-0.93333333333333313</v>
       </c>
-      <c r="E30" s="1">
+      <c r="H30" s="1">
         <v>5.6166666666666663E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1986</v>
       </c>
@@ -967,16 +4192,25 @@
         <v>317.27500000000003</v>
       </c>
       <c r="C31" s="1">
+        <v>7595.166666666667</v>
+      </c>
+      <c r="D31" s="1">
         <v>27.666666666666668</v>
       </c>
-      <c r="D31" s="1">
+      <c r="E31" s="1">
+        <v>28.00866666666667</v>
+      </c>
+      <c r="F31" s="1">
+        <v>27.60191683333333</v>
+      </c>
+      <c r="G31" s="1">
         <v>-8.3333333333333301E-2</v>
       </c>
-      <c r="E31" s="1">
+      <c r="H31" s="1">
         <v>-0.28533333333333338</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1985</v>
       </c>
@@ -984,16 +4218,25 @@
         <v>304.03333333333336</v>
       </c>
       <c r="C32" s="1">
+        <v>6495.833333333333</v>
+      </c>
+      <c r="D32" s="1">
         <v>27.466666666666665</v>
       </c>
-      <c r="D32" s="1">
+      <c r="E32" s="1">
+        <v>27.932500000000005</v>
+      </c>
+      <c r="F32" s="1">
+        <v>27.493508166666668</v>
+      </c>
+      <c r="G32" s="1">
         <v>0.28333333333333338</v>
       </c>
-      <c r="E32" s="1">
+      <c r="H32" s="1">
         <v>-0.27758333333333335</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1984</v>
       </c>
@@ -1001,16 +4244,25 @@
         <v>362.58333333333331</v>
       </c>
       <c r="C33" s="1">
+        <v>8824.1666666666661</v>
+      </c>
+      <c r="D33" s="1">
         <v>27.391666666666666</v>
       </c>
-      <c r="D33" s="1">
+      <c r="E33" s="1">
+        <v>28.216166666666666</v>
+      </c>
+      <c r="F33" s="1">
+        <v>27.776974750000004</v>
+      </c>
+      <c r="G33" s="1">
         <v>0.14166666666666666</v>
       </c>
-      <c r="E33" s="1">
+      <c r="H33" s="1">
         <v>-0.2183333333333333</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1983</v>
       </c>
@@ -1018,16 +4270,25 @@
         <v>157.01666666666668</v>
       </c>
       <c r="C34" s="1">
+        <v>5919.416666666667</v>
+      </c>
+      <c r="D34" s="1">
         <v>28.116666666666664</v>
       </c>
-      <c r="D34" s="1">
+      <c r="E34" s="1">
+        <v>28.491250000000004</v>
+      </c>
+      <c r="F34" s="1">
+        <v>28.261083500000009</v>
+      </c>
+      <c r="G34" s="1">
         <v>-0.7583333333333333</v>
       </c>
-      <c r="E34" s="1">
+      <c r="H34" s="1">
         <v>-8.1416666666666679E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1982</v>
       </c>
@@ -1035,16 +4296,25 @@
         <v>239.70833333333334</v>
       </c>
       <c r="C35" s="1">
+        <v>7746.166666666667</v>
+      </c>
+      <c r="D35" s="1">
         <v>27.591666666666669</v>
       </c>
-      <c r="D35" s="1">
+      <c r="E35" s="1">
+        <v>28.222583333333336</v>
+      </c>
+      <c r="F35" s="1">
+        <v>27.892187250000003</v>
+      </c>
+      <c r="G35" s="1">
         <v>-0.87500000000000011</v>
       </c>
-      <c r="E35" s="1">
+      <c r="H35" s="1">
         <v>-0.22341666666666668</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1981</v>
       </c>
@@ -1052,458 +4322,651 @@
         <v>256.24583333333334</v>
       </c>
       <c r="C36" s="1">
+        <v>9255.3333333333339</v>
+      </c>
+      <c r="D36" s="1">
         <v>27.858333333333334</v>
       </c>
-      <c r="D36" s="1">
+      <c r="E36" s="1"/>
+      <c r="F36" s="1">
+        <v>28.185258166666671</v>
+      </c>
+      <c r="G36" s="1">
         <v>0.24166666666666659</v>
       </c>
-      <c r="E36" s="1">
+      <c r="H36" s="1">
         <v>-8.7249999999999994E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1980</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1">
+        <v>6208.416666666667</v>
+      </c>
+      <c r="D37" s="1">
         <v>28.108333333333334</v>
       </c>
-      <c r="D37" s="1">
+      <c r="E37" s="1"/>
+      <c r="F37" s="1">
+        <v>28.043084333333326</v>
+      </c>
+      <c r="G37" s="1">
         <v>-6.6666666666666666E-2</v>
       </c>
-      <c r="E37" s="1">
+      <c r="H37" s="1">
         <v>-2.9499999999999998E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1979</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1">
+        <v>7326.75</v>
+      </c>
+      <c r="D38" s="1">
         <v>28.099999999999998</v>
       </c>
-      <c r="D38" s="1">
+      <c r="E38" s="1"/>
+      <c r="F38" s="1">
+        <v>28.02006891666667</v>
+      </c>
+      <c r="G38" s="1">
         <v>0.14166666666666669</v>
       </c>
-      <c r="E38" s="1">
+      <c r="H38" s="1">
         <v>-0.12133333333333333</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1978</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1">
+        <v>6900.75</v>
+      </c>
+      <c r="D39" s="1">
         <v>28.133333333333336</v>
       </c>
-      <c r="D39" s="1">
+      <c r="E39" s="1"/>
+      <c r="F39" s="1">
+        <v>27.956792916666668</v>
+      </c>
+      <c r="G39" s="1">
         <v>-6.6666666666666707E-2</v>
       </c>
-      <c r="E39" s="1">
+      <c r="H39" s="1">
         <v>-0.19074999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1977</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1">
+        <v>5718</v>
+      </c>
+      <c r="D40" s="1">
         <v>27.691666666666666</v>
       </c>
-      <c r="D40" s="1">
+      <c r="E40" s="1"/>
+      <c r="F40" s="1">
+        <v>27.782481666666659</v>
+      </c>
+      <c r="G40" s="1">
         <v>-0.63333333333333341</v>
       </c>
-      <c r="E40" s="1">
+      <c r="H40" s="1">
         <v>-0.20025000000000004</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1976</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1">
+        <v>7073.833333333333</v>
+      </c>
+      <c r="D41" s="1">
         <v>27.225000000000005</v>
       </c>
-      <c r="D41" s="1">
+      <c r="E41" s="1"/>
+      <c r="F41" s="1">
+        <v>27.514125249999996</v>
+      </c>
+      <c r="G41" s="1">
         <v>0.31666666666666671</v>
       </c>
-      <c r="E41" s="1">
+      <c r="H41" s="1">
         <v>-0.37458333333333343</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1975</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1">
+        <v>8841</v>
+      </c>
+      <c r="D42" s="1">
         <v>27.058333333333334</v>
       </c>
-      <c r="D42" s="1">
+      <c r="E42" s="1"/>
+      <c r="F42" s="1">
+        <v>27.521397249999993</v>
+      </c>
+      <c r="G42" s="1">
         <v>1.3333333333333333</v>
       </c>
-      <c r="E42" s="1">
+      <c r="H42" s="1">
         <v>-0.30933333333333335</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1974</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1">
+        <v>8906.5833333333339</v>
+      </c>
+      <c r="D43" s="1">
         <v>27.783333333333331</v>
       </c>
-      <c r="D43" s="1">
+      <c r="E43" s="1"/>
+      <c r="F43" s="1">
+        <v>27.591050083333329</v>
+      </c>
+      <c r="G43" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E43" s="1">
+      <c r="H43" s="1">
         <v>-0.4308333333333334</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1973</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1">
+        <v>6785.416666666667</v>
+      </c>
+      <c r="D44" s="1">
         <v>27.933333333333334</v>
       </c>
-      <c r="D44" s="1">
+      <c r="E44" s="1"/>
+      <c r="F44" s="1">
+        <v>28.083155250000001</v>
+      </c>
+      <c r="G44" s="1">
         <v>0.74166666666666659</v>
       </c>
-      <c r="E44" s="1">
+      <c r="H44" s="1">
         <v>-0.22575000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1972</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1">
+        <v>7173.75</v>
+      </c>
+      <c r="D45" s="1">
         <v>28.416666666666661</v>
       </c>
-      <c r="D45" s="1">
+      <c r="E45" s="1"/>
+      <c r="F45" s="1">
+        <v>27.894294000000002</v>
+      </c>
+      <c r="G45" s="1">
         <v>-0.48333333333333339</v>
       </c>
-      <c r="E45" s="1">
+      <c r="H45" s="1">
         <v>-0.36308333333333337</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1971</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1">
+        <v>10321.083333333334</v>
+      </c>
+      <c r="D46" s="1">
         <v>27.866666666666671</v>
       </c>
-      <c r="D46" s="1">
+      <c r="E46" s="1"/>
+      <c r="F46" s="1">
+        <v>27.711772416666673</v>
+      </c>
+      <c r="G46" s="1">
         <v>1.1083333333333336</v>
       </c>
-      <c r="E46" s="1">
+      <c r="H46" s="1">
         <v>-0.32100000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1970</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1">
+        <v>8388.8333333333339</v>
+      </c>
+      <c r="D47" s="1">
         <v>27.575000000000003</v>
       </c>
-      <c r="D47" s="1">
+      <c r="E47" s="1"/>
+      <c r="F47" s="1">
+        <v>28.054562916666669</v>
+      </c>
+      <c r="G47" s="1">
         <v>0.47499999999999992</v>
       </c>
-      <c r="E47" s="1">
+      <c r="H47" s="1">
         <v>-0.112</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1969</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1">
+        <v>7425.666666666667</v>
+      </c>
+      <c r="D48" s="1">
         <v>27.500000000000004</v>
       </c>
-      <c r="D48" s="1">
+      <c r="E48" s="1"/>
+      <c r="F48" s="1">
+        <v>28.485576833333329</v>
+      </c>
+      <c r="G48" s="1">
         <v>-0.35000000000000003</v>
       </c>
-      <c r="E48" s="1">
+      <c r="H48" s="1">
         <v>1.08333333333334E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1968</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="1">
+        <v>7191.583333333333</v>
+      </c>
+      <c r="D49" s="1">
         <v>27.258333333333336</v>
       </c>
-      <c r="D49" s="1">
+      <c r="E49" s="1"/>
+      <c r="F49" s="1">
+        <v>27.792016416666669</v>
+      </c>
+      <c r="G49" s="1">
         <v>0.39166666666666666</v>
       </c>
-      <c r="E49" s="1">
+      <c r="H49" s="1">
         <v>-0.17533333333333334</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1967</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1">
+        <v>7275.416666666667</v>
+      </c>
+      <c r="D50" s="1">
         <v>27.691666666666663</v>
       </c>
-      <c r="D50" s="1">
+      <c r="E50" s="1"/>
+      <c r="F50" s="1">
+        <v>27.820069250000003</v>
+      </c>
+      <c r="G50" s="1">
         <v>0.47500000000000003</v>
       </c>
-      <c r="E50" s="1">
+      <c r="H50" s="1">
         <v>-0.10599999999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1966</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1">
+        <v>7130.166666666667</v>
+      </c>
+      <c r="D51" s="1">
         <v>27.474999999999998</v>
       </c>
-      <c r="D51" s="1">
+      <c r="E51" s="1"/>
+      <c r="F51" s="1">
+        <v>28.103327749999995</v>
+      </c>
+      <c r="G51" s="1">
         <v>-0.21666666666666667</v>
       </c>
-      <c r="E51" s="1">
+      <c r="H51" s="1">
         <v>-3.6666666666666657E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1965</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1">
+        <v>5808.666666666667</v>
+      </c>
+      <c r="D52" s="1">
         <v>27.641666666666666</v>
       </c>
-      <c r="D52" s="1">
+      <c r="E52" s="1"/>
+      <c r="F52" s="1">
+        <v>27.66177708333333</v>
+      </c>
+      <c r="G52" s="1">
         <v>-0.5083333333333333</v>
       </c>
-      <c r="E52" s="1">
+      <c r="H52" s="1">
         <v>-0.16716666666666669</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1964</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="1">
+        <v>7291</v>
+      </c>
+      <c r="D53" s="1">
         <v>27.450000000000003</v>
       </c>
-      <c r="D53" s="1">
+      <c r="E53" s="1"/>
+      <c r="F53" s="1">
+        <v>27.907487833333331</v>
+      </c>
+      <c r="G53" s="1">
         <v>0.61666666666666659</v>
       </c>
-      <c r="E53" s="1">
+      <c r="H53" s="1">
         <v>-0.10299999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1963</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1">
+        <v>7493.166666666667</v>
+      </c>
+      <c r="D54" s="1">
         <v>27.841666666666669</v>
       </c>
-      <c r="D54" s="1">
+      <c r="E54" s="1"/>
+      <c r="F54" s="1">
+        <v>28.184613333333331</v>
+      </c>
+      <c r="G54" s="1">
         <v>-4.1666666666666664E-2</v>
       </c>
-      <c r="E54" s="1">
+      <c r="H54" s="1">
         <v>-2.8333333333333314E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1962</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1">
+        <v>7847.75</v>
+      </c>
+      <c r="D55" s="1">
         <v>27.858333333333331</v>
       </c>
-      <c r="D55" s="1">
+      <c r="E55" s="1"/>
+      <c r="F55" s="1">
+        <v>28.081928166666668</v>
+      </c>
+      <c r="G55" s="1">
         <v>0.53333333333333333</v>
       </c>
-      <c r="E55" s="1">
+      <c r="H55" s="1">
         <v>6.483333333333334E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1961</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1">
+        <v>6466</v>
+      </c>
+      <c r="D56" s="1">
         <v>27.341666666666665</v>
       </c>
-      <c r="D56" s="1">
+      <c r="E56" s="1"/>
+      <c r="F56" s="1">
+        <v>28.073719999999998</v>
+      </c>
+      <c r="G56" s="1">
         <v>0.18333333333333338</v>
       </c>
-      <c r="E56" s="1">
+      <c r="H56" s="1">
         <v>9.2833333333333337E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1960</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="1">
+        <v>7080.833333333333</v>
+      </c>
+      <c r="D57" s="1">
         <v>27.900000000000006</v>
       </c>
-      <c r="D57" s="1">
+      <c r="E57" s="1"/>
+      <c r="F57" s="1">
+        <v>28.333312166666662</v>
+      </c>
+      <c r="G57" s="1">
         <v>0.49999999999999994</v>
       </c>
-      <c r="E57" s="1">
+      <c r="H57" s="1">
         <v>0.22850000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1959</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1">
+        <v>5683.416666666667</v>
+      </c>
+      <c r="D58" s="1">
         <v>27.474999999999994</v>
       </c>
-      <c r="D58" s="1">
+      <c r="E58" s="1"/>
+      <c r="F58" s="1">
+        <v>27.908499250000002</v>
+      </c>
+      <c r="G58" s="1">
         <v>0.14166666666666669</v>
       </c>
-      <c r="E58" s="1">
+      <c r="H58" s="1">
         <v>4.6166666666666668E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1958</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1">
+        <v>4849.333333333333</v>
+      </c>
+      <c r="D59" s="1">
         <v>28.333333333333329</v>
       </c>
-      <c r="D59" s="1">
+      <c r="E59" s="1"/>
+      <c r="F59" s="1">
+        <v>28.570338916666667</v>
+      </c>
+      <c r="G59" s="1">
         <v>-0.15</v>
       </c>
-      <c r="E59" s="1">
+      <c r="H59" s="1">
         <v>0.20758333333333334</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1957</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1">
+        <v>5915.166666666667</v>
+      </c>
+      <c r="D60" s="1">
         <v>28.108333333333334</v>
       </c>
-      <c r="D60" s="1">
+      <c r="E60" s="1"/>
+      <c r="F60" s="1">
+        <v>27.858669166666669</v>
+      </c>
+      <c r="G60" s="1">
         <v>-0.17499999999999996</v>
       </c>
-      <c r="E60" s="1">
+      <c r="H60" s="1">
         <v>3.4166666666666658E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1956</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1">
+        <v>8566.4</v>
+      </c>
+      <c r="D61" s="1">
         <v>27.299999999999997</v>
       </c>
-      <c r="D61" s="1">
+      <c r="E61" s="1"/>
+      <c r="F61" s="1">
+        <v>27.715466666666668</v>
+      </c>
+      <c r="G61" s="1">
         <v>1.0916666666666668</v>
       </c>
-      <c r="E61" s="1">
+      <c r="H61" s="1">
         <v>-2.5416666666666667E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1955</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1">
+        <v>8441.6</v>
+      </c>
+      <c r="D62" s="1">
         <v>27.641666666666666</v>
       </c>
-      <c r="D62" s="1">
+      <c r="E62" s="1"/>
+      <c r="F62" s="1">
+        <v>27.859719916666666</v>
+      </c>
+      <c r="G62" s="1">
         <v>1.0250000000000001</v>
       </c>
-      <c r="E62" s="1">
+      <c r="H62" s="1">
         <v>0.18641666666666667</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1954</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1">
+        <v>7888.25</v>
+      </c>
+      <c r="D63" s="1">
         <v>27.833333333333339</v>
       </c>
-      <c r="D63" s="1">
+      <c r="E63" s="1"/>
+      <c r="F63" s="1">
+        <v>27.97646258333333</v>
+      </c>
+      <c r="G63" s="1">
         <v>0.44999999999999996</v>
       </c>
-      <c r="E63" s="1">
+      <c r="H63" s="1">
         <v>3.7249999999999998E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>1953</v>
-      </c>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>1952</v>
-      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>1951</v>
-      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>1950</v>
-      </c>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Data_processed/env_yr.xlsx
+++ b/Data_processed/env_yr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GDrive\Academicos\Articulos\Pendientes\Varadero growth rates\Data_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299EA2B4-71C7-4F21-8AFC-291A951100B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F6BFB4-30F7-4C80-A22D-9106B285C96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1392" yWindow="612" windowWidth="17280" windowHeight="10332" xr2:uid="{2EC6B3B9-CD09-474A-97A4-BF889824A090}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2EC6B3B9-CD09-474A-97A4-BF889824A090}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -122,7 +122,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -132,6 +132,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -148,10 +154,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4342,7 +4349,9 @@
       <c r="A37">
         <v>1980</v>
       </c>
-      <c r="B37" s="1"/>
+      <c r="B37" s="3">
+        <v>170.45690833333333</v>
+      </c>
       <c r="C37" s="1">
         <v>6208.416666666667</v>
       </c>
@@ -4364,7 +4373,9 @@
       <c r="A38">
         <v>1979</v>
       </c>
-      <c r="B38" s="1"/>
+      <c r="B38" s="3">
+        <v>207.25007499999995</v>
+      </c>
       <c r="C38" s="1">
         <v>7326.75</v>
       </c>
@@ -4386,7 +4397,9 @@
       <c r="A39">
         <v>1978</v>
       </c>
-      <c r="B39" s="1"/>
+      <c r="B39" s="3">
+        <v>193.23467500000001</v>
+      </c>
       <c r="C39" s="1">
         <v>6900.75</v>
       </c>
@@ -4408,7 +4421,9 @@
       <c r="A40">
         <v>1977</v>
       </c>
-      <c r="B40" s="1"/>
+      <c r="B40" s="3">
+        <v>154.32220000000001</v>
+      </c>
       <c r="C40" s="1">
         <v>5718</v>
       </c>
@@ -4430,7 +4445,9 @@
       <c r="A41">
         <v>1976</v>
       </c>
-      <c r="B41" s="1"/>
+      <c r="B41" s="3">
+        <v>198.92911666666669</v>
+      </c>
       <c r="C41" s="1">
         <v>7073.833333333333</v>
       </c>
@@ -4452,7 +4469,9 @@
       <c r="A42">
         <v>1975</v>
       </c>
-      <c r="B42" s="1"/>
+      <c r="B42" s="3">
+        <v>257.06890000000004</v>
+      </c>
       <c r="C42" s="1">
         <v>8841</v>
       </c>
@@ -4474,7 +4493,9 @@
       <c r="A43">
         <v>1974</v>
       </c>
-      <c r="B43" s="1"/>
+      <c r="B43" s="3">
+        <v>259.22659166666671</v>
+      </c>
       <c r="C43" s="1">
         <v>8906.5833333333339</v>
       </c>
@@ -4496,7 +4517,9 @@
       <c r="A44">
         <v>1973</v>
       </c>
-      <c r="B44" s="1"/>
+      <c r="B44" s="3">
+        <v>189.44020833333332</v>
+      </c>
       <c r="C44" s="1">
         <v>6785.416666666667</v>
       </c>
@@ -4518,7 +4541,9 @@
       <c r="A45">
         <v>1972</v>
       </c>
-      <c r="B45" s="1"/>
+      <c r="B45" s="3">
+        <v>202.21637499999997</v>
+      </c>
       <c r="C45" s="1">
         <v>7173.75</v>
       </c>
@@ -4540,7 +4565,9 @@
       <c r="A46">
         <v>1971</v>
       </c>
-      <c r="B46" s="1"/>
+      <c r="B46" s="3">
+        <v>305.76364166666662</v>
+      </c>
       <c r="C46" s="1">
         <v>10321.083333333334</v>
       </c>
@@ -4562,7 +4589,9 @@
       <c r="A47">
         <v>1970</v>
       </c>
-      <c r="B47" s="1"/>
+      <c r="B47" s="3">
+        <v>242.19261666666662</v>
+      </c>
       <c r="C47" s="1">
         <v>8388.8333333333339</v>
       </c>
@@ -4584,7 +4613,9 @@
       <c r="A48">
         <v>1969</v>
       </c>
-      <c r="B48" s="1"/>
+      <c r="B48" s="3">
+        <v>210.50443333333328</v>
+      </c>
       <c r="C48" s="1">
         <v>7425.666666666667</v>
       </c>
@@ -4606,7 +4637,9 @@
       <c r="A49">
         <v>1968</v>
       </c>
-      <c r="B49" s="1"/>
+      <c r="B49" s="3">
+        <v>202.80309166666666</v>
+      </c>
       <c r="C49" s="1">
         <v>7191.583333333333</v>
       </c>
@@ -4628,7 +4661,9 @@
       <c r="A50">
         <v>1967</v>
       </c>
-      <c r="B50" s="1"/>
+      <c r="B50" s="3">
+        <v>205.56120833333333</v>
+      </c>
       <c r="C50" s="1">
         <v>7275.416666666667</v>
       </c>
@@ -4650,7 +4685,9 @@
       <c r="A51">
         <v>1966</v>
       </c>
-      <c r="B51" s="1"/>
+      <c r="B51" s="3">
+        <v>200.78248333333332</v>
+      </c>
       <c r="C51" s="1">
         <v>7130.166666666667</v>
       </c>
@@ -4672,7 +4709,9 @@
       <c r="A52">
         <v>1965</v>
       </c>
-      <c r="B52" s="1"/>
+      <c r="B52" s="3">
+        <v>157.30513333333332</v>
+      </c>
       <c r="C52" s="1">
         <v>5808.666666666667</v>
       </c>
@@ -4694,7 +4733,9 @@
       <c r="A53">
         <v>1964</v>
       </c>
-      <c r="B53" s="1"/>
+      <c r="B53" s="3">
+        <v>206.07389999999995</v>
+      </c>
       <c r="C53" s="1">
         <v>7291</v>
       </c>
@@ -4716,7 +4757,9 @@
       <c r="A54">
         <v>1963</v>
       </c>
-      <c r="B54" s="1"/>
+      <c r="B54" s="3">
+        <v>212.72518333333332</v>
+      </c>
       <c r="C54" s="1">
         <v>7493.166666666667</v>
       </c>
@@ -4738,7 +4781,9 @@
       <c r="A55">
         <v>1962</v>
       </c>
-      <c r="B55" s="1"/>
+      <c r="B55" s="3">
+        <v>224.390975</v>
+      </c>
       <c r="C55" s="1">
         <v>7847.75</v>
       </c>
@@ -4760,7 +4805,9 @@
       <c r="A56">
         <v>1961</v>
       </c>
-      <c r="B56" s="1"/>
+      <c r="B56" s="3">
+        <v>178.93139999999994</v>
+      </c>
       <c r="C56" s="1">
         <v>6466</v>
       </c>
@@ -4782,7 +4829,9 @@
       <c r="A57">
         <v>1960</v>
       </c>
-      <c r="B57" s="1"/>
+      <c r="B57" s="3">
+        <v>199.15941666666663</v>
+      </c>
       <c r="C57" s="1">
         <v>7080.833333333333</v>
       </c>
@@ -4804,7 +4853,9 @@
       <c r="A58">
         <v>1959</v>
       </c>
-      <c r="B58" s="1"/>
+      <c r="B58" s="3">
+        <v>153.18440833333332</v>
+      </c>
       <c r="C58" s="1">
         <v>5683.416666666667</v>
       </c>
@@ -4826,7 +4877,9 @@
       <c r="A59">
         <v>1958</v>
       </c>
-      <c r="B59" s="1"/>
+      <c r="B59" s="3">
+        <v>125.74306666666665</v>
+      </c>
       <c r="C59" s="1">
         <v>4849.333333333333</v>
       </c>
@@ -4848,7 +4901,9 @@
       <c r="A60">
         <v>1957</v>
       </c>
-      <c r="B60" s="1"/>
+      <c r="B60" s="3">
+        <v>160.80898333333334</v>
+      </c>
       <c r="C60" s="1">
         <v>5915.166666666667</v>
       </c>
@@ -4870,7 +4925,9 @@
       <c r="A61">
         <v>1956</v>
       </c>
-      <c r="B61" s="1"/>
+      <c r="B61" s="3">
+        <v>248.03455999999997</v>
+      </c>
       <c r="C61" s="1">
         <v>8566.4</v>
       </c>
@@ -4892,7 +4949,9 @@
       <c r="A62">
         <v>1955</v>
       </c>
-      <c r="B62" s="1"/>
+      <c r="B62" s="3">
+        <v>243.92863999999994</v>
+      </c>
       <c r="C62" s="1">
         <v>8441.6</v>
       </c>
@@ -4914,7 +4973,9 @@
       <c r="A63">
         <v>1954</v>
       </c>
-      <c r="B63" s="1"/>
+      <c r="B63" s="3">
+        <v>225.72342500000002</v>
+      </c>
       <c r="C63" s="1">
         <v>7888.25</v>
       </c>
